--- a/astro-site/public/dl/sushi-restaurant-business-plan/sushi-restaurant-financial-projections.xlsx
+++ b/astro-site/public/dl/sushi-restaurant-business-plan/sushi-restaurant-financial-projections.xlsx
@@ -826,7 +826,7 @@
         <v>35.1</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, "&amp;"menu prices include VAT.","")</f>
+        <f>IFERROR("Average check excl. sales tax plus the weighted sales tax of your sales lines ("&amp;TEXT(SUMPRODUCT('3-Year P&amp;L'!$E$10:$E$11,'3-Year P&amp;L'!$G$10:$G$11)*100,"0")&amp;"%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. "&amp;"In the UK, menu prices include VAT.","")</f>
         <v>Average check excl. sales tax plus the weighted sales tax of your sales lines (8%), rounded. In the US, menu prices usually exclude sales tax and it is added at the register; the beverage share in column H of the beverage line of the P&amp;L only moves this average if your state taxes alcohol at another rate. In the UK, menu prices include VAT.</v>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="B38" s="29" t="inlineStr">
         <is>
-          <t>Theoretical cost of each nigiri, roll and platter by channel</t>
+          <t>Salmon nigiri about 23%, California roll about 12%, spicy tuna roll about 39%; whole menu about 24%</t>
         </is>
       </c>
       <c r="C38" s="29" t="inlineStr">
@@ -7305,7 +7305,7 @@
       </c>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>The plan's 32% is the real usage of the whole menu, waste included, so it comes out higher than the cost per piece</t>
+          <t>The plan's 32% is the real usage of the whole menu, with case shrink, trim, rice thrown out and staff meals: it comes out higher than the theoretical cost per piece</t>
         </is>
       </c>
       <c r="E38" s="29" t="n"/>

--- a/astro-site/public/dl/sushi-restaurant-business-plan/sushi-restaurant-financial-projections.xlsx
+++ b/astro-site/public/dl/sushi-restaurant-business-plan/sushi-restaurant-financial-projections.xlsx
@@ -766,7 +766,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Per cover, EXCL. sales tax and tip: a dine-in guest spends about $36.00 (food $28.50 plus beverage $7.50); a take-out order averages $41.00 and a marketplace order $46.00 (the menu is about 15% higher there and the order a bit bigger). At 1.6 covers per order, that is $25.60 and $28.75 per cover, and the weighted average of the three channels is $32.48; the example rounds it to $32.50 (Kit estimate). The "Menu price incl. sales tax (calculated)" row below shows the price with your local rate applied</t>
+          <t>Per cover, EXCL. sales tax and tip: a dine-in guest spends about $36.00 (food $28.50 plus beverage $7.50); a take-out order averages $41.00 and a marketplace order $46.00 (the menu is about 15% higher there, for about the same basket). At 1.6 covers per order, that is $25.63 and $28.75 per cover, and the weighted average of the three channels is $32.48; the example rounds it to $32.50 (Kit estimate). The "Menu price incl. sales tax (calculated)" row below shows the price with your local rate applied</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="D14" s="29" t="inlineStr">
         <is>
-          <t>The parasite rule (FDA Food Code 3-402.11) asks for raw fish to be frozen at −4 °F or below for 7 days, or at −31 °F until solid plus 15 hours, or at −31 °F until solid plus 24 hours at −4 °F. Tuna and feed-raised aquaculture fish are exempt with a written supplier statement, and records are kept 90 days. This freezer HOLDS the fish you buy already treated, at −4 °F or below with a logger; freezing fish yourself takes a lot of freezer space. Kit estimate: ask for the data sheet</t>
+          <t>The parasite rule (FDA Food Code 3-402.11) asks for raw fish to be frozen at −4 °F or below for 7 days, or at −31 °F until solid plus 15 hours, or at −31 °F until solid plus 24 hours at −4 °F. Tuna is exempt, and so is feed-raised aquaculture fish with a written supplier statement; records are kept 90 days. This freezer HOLDS the fish you buy already treated, at −4 °F or below with a logger; freezing fish yourself takes a lot of freezer space. Kit estimate: ask for the data sheet</t>
         </is>
       </c>
       <c r="E14" s="32" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="J5" s="29" t="inlineStr">
         <is>
-          <t>Buys from the fish suppliers and files their letters, runs the floor and the delivery marketplaces and manages. In the US the owner is not the one at the sushi bar: you hire the head sushi chef (next row). The workbook imputes a monthly salary as if on payroll, which is the prudent side; confirm with your CPA how you will pay yourself (owner's draw or W-2 under an S corp). The example pays the owner below a manager: owner's draw in addition from net profit</t>
+          <t>Buys from the fish suppliers and files their letters, runs the floor and the delivery marketplaces and manages. In this plan the owner is not the one at the sushi bar: you hire the head sushi chef (next row). The workbook imputes a monthly salary as if on payroll, which is the prudent side; confirm with your CPA how you will pay yourself (owner's draw or W-2 under an S corp). The example pays the owner below a manager: owner's draw in addition from net profit</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="J11" s="29" t="inlineStr">
         <is>
-          <t>Coverage for vacations and the team's days off through the year. Paid sick leave is required by some states and cities: check yours</t>
+          <t>Dishwashing, rice washing and prep: about $16 per hour in the example. Vacations and days off are already counted in the weeks worked per person below. Paid sick leave is required by some states and cities: check yours</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       <c r="I21" s="29" t="n"/>
       <c r="J21" s="29" t="inlineStr">
         <is>
-          <t>Hours the restaurant is open to the public, adding lunch (11:30-14:30) and dinner (17:00-21:30; 22:00 on Friday and Saturday). The afternoon between the two services is not counted</t>
+          <t>Hours the restaurant is open to the public, adding lunch (11:30 a.m. to 2:30 p.m.) and dinner (5:00 to 9:30 p.m.; 10:00 p.m. on Friday and Saturday). The afternoon between the two services is not counted</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
     <row r="7" ht="105" customHeight="1">
       <c r="A7" s="48" t="inlineStr">
         <is>
-          <t>3. On "Break-Even" you only type the seat-turn ceiling your space allows; everything else derives from the rest. The other three tabs also have green cells you can change: the pessimistic and optimistic scenarios on "Scenarios", the seasonality and the launch ramp-up on "12-Month Cash Flow", and the other financing sources on "Financing" (rows 8-11 count as sources but are not amortized: Your bank or SBA 7(a) loan goes in "Loan requested" on "0. Assumptions"). Everything else is calculated.</t>
+          <t>3. On "Break-Even" you only type the seat-turn ceiling your space allows; everything else derives from the rest. The other three tabs also have green cells you can change: the pessimistic and optimistic scenarios on "Scenarios", the seasonality and the launch ramp-up on "12-Month Cash Flow", and the other financing sources on "Financing" (rows 8-11 count as sources but are not amortized: your bank or SBA 7(a) loan goes in "Loan requested" on "0. Assumptions"). Everything else is calculated.</t>
         </is>
       </c>
       <c r="B7" s="29" t="n"/>
